--- a/data/03_final/GenAI_MetaAnalysis_v5.xlsx
+++ b/data/03_final/GenAI_MetaAnalysis_v5.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,8 @@
           <t>Unique study identifier</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Integer (1-70)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,19 +463,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Effect size identifier within study</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Format: XXX_YY</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
+          <t>Effect size identifier</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,16 +480,8 @@
           <t>Study title</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,16 +494,8 @@
           <t>Publication year</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2020-2025</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -540,16 +508,8 @@
           <t>Study authors</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -559,19 +519,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Name of outcome measure</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Outcome measure name</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -581,19 +533,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Outcome category (cognitive/affective/behavioral)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>cognitive/affective/behavioral</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Coded</t>
-        </is>
-      </c>
+          <t>Outcome category</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -606,16 +550,8 @@
           <t>Blooms taxonomy level</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>lower_order/higher_order</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Coded</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -625,19 +561,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Treatment group sample size</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Treatment group n</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -647,19 +575,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Control group sample size</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Control group n</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -669,19 +589,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Treatment group mean</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Treatment mean</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -691,19 +603,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Treatment group SD</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Treatment SD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -713,19 +617,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Control group mean</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Control mean</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -735,19 +631,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Control group SD</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
+          <t>Control SD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -760,16 +648,8 @@
           <t>Hedges g effect size</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Numeric (-3 to 3)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -779,19 +659,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Standard error of g</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Numeric (&gt;0)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
+          <t>Standard error</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -804,16 +676,8 @@
           <t>Verification status</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>OCR_VERIFIED/MANUAL/NOT_CHECKED</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Coded</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -823,19 +687,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Confidence in verification (0-100)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Coded</t>
-        </is>
-      </c>
+          <t>Verification confidence</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -845,19 +701,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Data quality tier (1-3)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1/2/3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Coded</t>
-        </is>
-      </c>
+          <t>Data quality tier</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GenAI_Tool</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GenAI tool used</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Study_Design</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Study design type</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -870,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,15 +772,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Sample_Size</t>
+          <t>GenAI_Tool</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outcomes</t>
+          <t>n_Treatment</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>Outcome_Dimension</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_Effects</t>
         </is>
@@ -927,15 +808,20 @@
           <t>Jiyong Chun; Jeongsoo Kim; Hyejin Kim; Geumgu Lee; Sanggoo Cho; Changshik Kim; Yeesook Chung; Seoyoon Heo</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>cognitive, behavioral, affective</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -956,15 +842,20 @@
           <t>Hui He; Xing Li</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>38</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -981,15 +872,20 @@
         <v>2025</v>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>25</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1010,15 +906,20 @@
           <t>Isaac Sung Him Ng; Anthony Siu; Chul Hwan Han; Oscar Sing Him Ho; Jonathan Sun; Anatoliy Markiv; Stuart Knight; Mandeep Gill Sagoo</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>20</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>affective, cognitive</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1039,15 +940,20 @@
           <t>Mohammed Ahmed Kofahi; A. Husain</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>23</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1068,15 +974,20 @@
           <t>Hui Hong; Poonsri Vate-U-Lan; Chantana Viriyavejakul</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>120</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>cognitive, behavioral</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1097,9 +1008,14 @@
           <t>Wesley Wu-Yi Koo</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1120,15 +1036,20 @@
           <t>Litian Hong</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>210</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>cognitive, behavioral</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1145,15 +1066,20 @@
         <v>2025</v>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>20</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>cognitive, affective, behavioral</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1174,15 +1100,20 @@
           <t>Kai Zhang</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>125</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>cognitive, affective, behavioral</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1203,15 +1134,20 @@
           <t>Jiamu Zeng; Kexin Sun; Peng Qin; Shulin Liu</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>72</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>cognitive, behavioral</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1232,15 +1168,20 @@
           <t>Xiaoqing Xu; Lifang Qiao; Nuo Cheng; Hongxia Liu; Wei Zhao</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>35</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>cognitive, metacognitive, affective</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1261,15 +1202,20 @@
           <t>Rufeng Chen; Shuaishuai Jiang; Jiyun Shen; AJung Moon; Lili Wei</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1290,15 +1236,20 @@
           <t>Yabing Jiang; Kazuo Nakatani</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>30</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1319,15 +1270,20 @@
           <t>Guoqing Zhao; Haixi Sheng; Yaxuan Wang; Xiaohui Cai; Taotao Long</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>89</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1348,15 +1304,20 @@
           <t>Yu Ji; Zehui Zhan; Tingting Li; Xuanxuan Zou; Siyuan Lyu</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>21</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>cognitive, metacognitive, affective</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1377,13 +1338,18 @@
           <t>Larissa I. Velez; Christian Alis; Christopher Monterola; Erika Fille Legara; David Stanley</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1404,15 +1370,20 @@
           <t>Viktor Taneski; Sašo Karakatič; Patrik Rek; Gregor Jošt</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>32</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1433,13 +1404,18 @@
           <t>Ruiwei Xiao; Xinying Hou; Runlong Ye; Majeed Kazemitabaar; Nicholas Diana; Michael Liut; John Stamper</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1460,15 +1436,20 @@
           <t>Ting-Ting Wu; Hsin-Yu Lee; Pei-Hua Chen; Chia-Ju Lin; Yueh-Min Huang</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>31</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1485,15 +1466,20 @@
         <v>2025</v>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>60</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1514,15 +1500,20 @@
           <t>Rafal Wlodarski; Leonardo da Silva Sousa; Allison Connell Pensky</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>17</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>behavioral, cognitive, affective, metacognitive</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1543,15 +1534,20 @@
           <t>Tuan Cong Le; Nguyen Dat Minh; Minh Dũng Tăng; Van Trinh; Nhut Minh Nguyen</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>33</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>affective, behavioral</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1572,9 +1568,14 @@
           <t>Ben Degen</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-4o)</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1595,15 +1596,20 @@
           <t>Mahir Akgün; Şacip Toker</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>29</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1624,15 +1630,20 @@
           <t>Mai Al-Otaibi; Khalid Mohamed Al-Homidhi</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>30</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1653,15 +1664,20 @@
           <t>Ching-Yi Chang; Wen-Song Su</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>33</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1682,15 +1698,20 @@
           <t>Haneen Saad Salman; Farid Saleh Fayyad</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>30</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1711,15 +1732,20 @@
           <t>Nataliya Kasimovskaya</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>75</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>cognitive, behavioral, affective</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1740,15 +1766,20 @@
           <t>Renfeng Jiang; Yang Gang; Shen Qi</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>168</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>affective</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1769,15 +1800,20 @@
           <t>Wafa Muhammad; Dr. Farooq Nawaz Khan; Akhtar Hussain; Farkhanda Nazli</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>27</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>cognitive, metacognitive</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1798,15 +1834,20 @@
           <t>Dariya Ovsyannikova; Victoria Oldemburgo de Mello; Michael Inzlicht</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>54</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>affective</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1827,9 +1868,14 @@
           <t>Hartwig H. Hochmair</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1850,15 +1896,20 @@
           <t>Yvonne Tiandem-Adamou</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>100</v>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1879,15 +1930,20 @@
           <t>Jin‐Hee Han; Ruqin Ren</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>40</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>cognitive, behavioral</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1908,15 +1964,20 @@
           <t>Atakan Coban; David Dzsotjan; Stefan Küchemann; Jürgen Durst; Jochen Kuhn; Christoph Hoyer</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>11</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1937,15 +1998,20 @@
           <t>Haixin Liu</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>15</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1966,15 +2032,20 @@
           <t>Dadan Dasari; Agus Hendriyanto; Sani Sahara; Didi Suryadi; Lukman Hakim Muhaimin; Theodore Chao; Laila Fitriana</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>9</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1995,13 +2066,18 @@
           <t>Nely Rahmawati Zaimah; Fatchiatuzahro Fatchiatuzahro; Eko Hartanto</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2022,15 +2098,20 @@
           <t>Hsin-Yu Lee; Pei-Hua Chen; Wei-Sheng Wang; Yueh-Min Huang; Ting-Ting Wu</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>31</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>metacognitive, cognitive</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2051,15 +2132,20 @@
           <t>Sireesha Prathigadapa; Salwani Binti Mohd Daud; Bryan Thien Chek Hui; Morampudi Rama Tulasi Raju</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>170</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2080,15 +2166,20 @@
           <t>Sumie Chan; N. Lo; Alan Wong</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>GPT-3.5-turbo</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>342</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>cognitive, affective, behavioral</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2109,15 +2200,20 @@
           <t>Kartika S</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>40</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2138,15 +2234,20 @@
           <t>Shalong Wang; Zuo Yi; Zou Bin; Ganglei Liu; Zhou Jinyu; Yanwen Zheng; Zhang Zequn; Lianwen Yuan; Ren Feng</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>50</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>metacognitive, cognitive, affective</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2167,13 +2268,18 @@
           <t>Sumie Chan; Noble Lo; Alan S.L. Wong</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>cognitive, affective, behavioral</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2190,15 +2296,20 @@
         <v>2024</v>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>32</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>cognitive, affective, metacognitive</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2219,15 +2330,20 @@
           <t>Santosh Mahapatra</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>37</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2248,15 +2364,20 @@
           <t>Yousef Wardat</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>55</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2277,9 +2398,14 @@
           <t>Harsh Kumar; Ruiwei Xiao; Benjamin Lawson; Ilya Musabirov; Jiakai Shi; Xinyuan Wang; Huayin Luo; J. Williams; Anna N. Rafferty; John Stamper; Michael Liut</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2300,9 +2426,14 @@
           <t>Lixiang Yan; Roberto Martinez-Maldonado; Yueqiao Jin; Vanessa Echeverria; Mikaela Milesi; Jie Fan; Linxuan Zhao; Riordan Alfredo; Xinyu Li; Dragan Gašević</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2323,15 +2454,20 @@
           <t>Hyewon Shin; J. C. De Gagne; Sang Suk Kim; Minjoo Hong</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
         <v>52</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>affective, cognitive, behavioral, metacognitive</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2348,15 +2484,20 @@
         <v>2024</v>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>25</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2377,9 +2518,14 @@
           <t>Alexandre Hudon; Barnabé Kiepura; Myriam Pelletier; Véronique Phan</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2396,15 +2542,20 @@
         <v>2023</v>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>39</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2425,15 +2576,20 @@
           <t>Muhammad Hakiki; Radinal Fadli; A. Samala; Ade Fricticarani; Popi Dayurni; Kurniati Rahmadani; Ayu Dewi Astiti</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>31</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>cognitive, behavioral</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2454,15 +2610,20 @@
           <t>Julia M. Markel; Steven G. Opferman; J. Landay; C. Piech</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>5</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>affective</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2483,13 +2644,18 @@
           <t>Ying Guo; Daniel Lee</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2510,13 +2676,18 @@
           <t>María-Isabel de Vicente-Yagüe-Jara; Olivia López-Martínez; Verónica Navarro-Navarro; Francisco Cuéllar-Santiago</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2533,9 +2704,14 @@
         <v>2018</v>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="n">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2550,15 +2726,20 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>38</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>cognitive</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2579,15 +2760,16 @@
           <t>Ramazan Yilmaz; Fatma Gizem Karaoglan Yilmaz</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
         <v>21</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>cognitive, affective</t>
         </is>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2602,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S347"/>
+  <dimension ref="A1:U347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2701,6 +2883,16 @@
           <t>Data_Tier</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>GenAI_Tool</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Study_Design</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2770,6 +2962,16 @@
       <c r="S2" t="n">
         <v>3</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2839,6 +3041,16 @@
       <c r="S3" t="n">
         <v>3</v>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2908,6 +3120,16 @@
       <c r="S4" t="n">
         <v>3</v>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2977,6 +3199,16 @@
       <c r="S5" t="n">
         <v>3</v>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3049,6 +3281,16 @@
       </c>
       <c r="S6" t="n">
         <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3111,6 +3353,16 @@
       <c r="S7" t="n">
         <v>1</v>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3172,6 +3424,16 @@
       <c r="S8" t="n">
         <v>1</v>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3241,6 +3503,16 @@
       <c r="S9" t="n">
         <v>3</v>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3310,6 +3582,16 @@
       <c r="S10" t="n">
         <v>3</v>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3379,6 +3661,16 @@
       <c r="S11" t="n">
         <v>3</v>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3448,6 +3740,16 @@
       <c r="S12" t="n">
         <v>3</v>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3517,6 +3819,16 @@
       <c r="S13" t="n">
         <v>3</v>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3586,6 +3898,16 @@
       <c r="S14" t="n">
         <v>3</v>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3659,6 +3981,16 @@
       <c r="S15" t="n">
         <v>3</v>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3732,6 +4064,16 @@
       <c r="S16" t="n">
         <v>3</v>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3805,6 +4147,16 @@
       <c r="S17" t="n">
         <v>3</v>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3878,6 +4230,16 @@
       <c r="S18" t="n">
         <v>3</v>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3947,6 +4309,16 @@
       <c r="S19" t="n">
         <v>3</v>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4016,6 +4388,16 @@
       <c r="S20" t="n">
         <v>3</v>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4089,6 +4471,16 @@
       <c r="S21" t="n">
         <v>3</v>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4162,6 +4554,16 @@
       <c r="S22" t="n">
         <v>3</v>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4235,6 +4637,16 @@
       <c r="S23" t="n">
         <v>3</v>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4308,6 +4720,16 @@
       <c r="S24" t="n">
         <v>1</v>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4379,6 +4801,16 @@
       <c r="S25" t="n">
         <v>1</v>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4450,6 +4882,16 @@
       <c r="S26" t="n">
         <v>1</v>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4521,6 +4963,16 @@
       <c r="S27" t="n">
         <v>1</v>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4592,6 +5044,16 @@
       <c r="S28" t="n">
         <v>1</v>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4663,6 +5125,16 @@
       <c r="S29" t="n">
         <v>1</v>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4733,6 +5205,16 @@
       </c>
       <c r="S30" t="n">
         <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -4790,6 +5272,16 @@
       </c>
       <c r="S31" t="n">
         <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -4836,6 +5328,16 @@
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4909,6 +5411,16 @@
       <c r="S33" t="n">
         <v>2</v>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4982,6 +5494,16 @@
       <c r="S34" t="n">
         <v>2</v>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5055,6 +5577,16 @@
       <c r="S35" t="n">
         <v>2</v>
       </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5128,6 +5660,16 @@
       <c r="S36" t="n">
         <v>2</v>
       </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5197,6 +5739,16 @@
       <c r="S37" t="n">
         <v>2</v>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5269,6 +5821,16 @@
       </c>
       <c r="S38" t="n">
         <v>2</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -5328,6 +5890,16 @@
       </c>
       <c r="S39" t="n">
         <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5386,6 +5958,16 @@
       <c r="S40" t="n">
         <v>1</v>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5440,6 +6022,16 @@
       </c>
       <c r="S41" t="n">
         <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -5494,6 +6086,16 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5548,6 +6150,16 @@
       </c>
       <c r="S43" t="n">
         <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -5610,6 +6222,16 @@
       <c r="S44" t="n">
         <v>1</v>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5671,6 +6293,16 @@
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5732,6 +6364,16 @@
       <c r="S46" t="n">
         <v>1</v>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5793,6 +6435,16 @@
       <c r="S47" t="n">
         <v>1</v>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5850,6 +6502,16 @@
       <c r="S48" t="n">
         <v>1</v>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5907,6 +6569,16 @@
       <c r="S49" t="n">
         <v>1</v>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5964,6 +6636,16 @@
       <c r="S50" t="n">
         <v>1</v>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6021,6 +6703,16 @@
       <c r="S51" t="n">
         <v>1</v>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6089,6 +6781,16 @@
       </c>
       <c r="S52" t="n">
         <v>1</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -6145,6 +6847,16 @@
       <c r="S53" t="n">
         <v>1</v>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6218,6 +6930,16 @@
       <c r="S54" t="n">
         <v>1</v>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6286,6 +7008,16 @@
       </c>
       <c r="S55" t="n">
         <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -6348,6 +7080,16 @@
       <c r="S56" t="n">
         <v>1</v>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6409,6 +7151,16 @@
       <c r="S57" t="n">
         <v>1</v>
       </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6478,6 +7230,16 @@
       <c r="S58" t="n">
         <v>1</v>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6547,6 +7309,16 @@
       <c r="S59" t="n">
         <v>1</v>
       </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6616,6 +7388,16 @@
       <c r="S60" t="n">
         <v>1</v>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6685,6 +7467,16 @@
       <c r="S61" t="n">
         <v>1</v>
       </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6754,6 +7546,16 @@
       <c r="S62" t="n">
         <v>1</v>
       </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6822,6 +7624,16 @@
       </c>
       <c r="S63" t="n">
         <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -6880,6 +7692,16 @@
       <c r="S64" t="n">
         <v>1</v>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6937,6 +7759,16 @@
       <c r="S65" t="n">
         <v>1</v>
       </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6994,6 +7826,16 @@
       <c r="S66" t="n">
         <v>1</v>
       </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7059,6 +7901,16 @@
       <c r="S67" t="n">
         <v>1</v>
       </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7124,6 +7976,16 @@
       <c r="S68" t="n">
         <v>1</v>
       </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7195,6 +8057,16 @@
       <c r="S69" t="n">
         <v>1</v>
       </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7266,6 +8138,16 @@
       <c r="S70" t="n">
         <v>1</v>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7337,6 +8219,16 @@
       <c r="S71" t="n">
         <v>1</v>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7408,6 +8300,16 @@
       <c r="S72" t="n">
         <v>1</v>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7479,6 +8381,16 @@
       <c r="S73" t="n">
         <v>1</v>
       </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7550,6 +8462,16 @@
       <c r="S74" t="n">
         <v>1</v>
       </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7621,6 +8543,16 @@
       <c r="S75" t="n">
         <v>1</v>
       </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7694,6 +8626,16 @@
       <c r="S76" t="n">
         <v>2</v>
       </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -7767,6 +8709,16 @@
       <c r="S77" t="n">
         <v>2</v>
       </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -7840,6 +8792,16 @@
       <c r="S78" t="n">
         <v>1</v>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7913,6 +8875,16 @@
       <c r="S79" t="n">
         <v>1</v>
       </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7986,6 +8958,16 @@
       <c r="S80" t="n">
         <v>1</v>
       </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8059,6 +9041,16 @@
       <c r="S81" t="n">
         <v>1</v>
       </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8128,6 +9120,16 @@
       <c r="S82" t="n">
         <v>1</v>
       </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8197,6 +9199,16 @@
       <c r="S83" t="n">
         <v>1</v>
       </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8266,6 +9278,16 @@
       <c r="S84" t="n">
         <v>1</v>
       </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8339,6 +9361,16 @@
       <c r="S85" t="n">
         <v>1</v>
       </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8412,6 +9444,16 @@
       <c r="S86" t="n">
         <v>1</v>
       </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -8485,6 +9527,16 @@
       <c r="S87" t="n">
         <v>1</v>
       </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -8558,6 +9610,16 @@
       <c r="S88" t="n">
         <v>1</v>
       </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -8631,6 +9693,16 @@
       <c r="S89" t="n">
         <v>1</v>
       </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -8703,6 +9775,16 @@
       </c>
       <c r="S90" t="n">
         <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -8761,6 +9843,16 @@
       <c r="S91" t="n">
         <v>1</v>
       </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -8826,6 +9918,16 @@
       <c r="S92" t="n">
         <v>1</v>
       </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -8891,6 +9993,16 @@
       <c r="S93" t="n">
         <v>1</v>
       </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -8956,6 +10068,16 @@
       <c r="S94" t="n">
         <v>1</v>
       </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9021,6 +10143,16 @@
       <c r="S95" t="n">
         <v>1</v>
       </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9086,6 +10218,16 @@
       <c r="S96" t="n">
         <v>1</v>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9151,6 +10293,16 @@
       <c r="S97" t="n">
         <v>1</v>
       </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -9216,6 +10368,16 @@
       <c r="S98" t="n">
         <v>1</v>
       </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -9281,6 +10443,16 @@
       <c r="S99" t="n">
         <v>1</v>
       </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -9346,6 +10518,16 @@
       <c r="S100" t="n">
         <v>1</v>
       </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -9411,6 +10593,16 @@
       <c r="S101" t="n">
         <v>1</v>
       </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -9476,6 +10668,16 @@
       <c r="S102" t="n">
         <v>1</v>
       </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -9549,6 +10751,16 @@
       <c r="S103" t="n">
         <v>2</v>
       </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -9622,6 +10834,16 @@
       <c r="S104" t="n">
         <v>2</v>
       </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -9695,6 +10917,16 @@
       <c r="S105" t="n">
         <v>2</v>
       </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -9768,6 +11000,16 @@
       <c r="S106" t="n">
         <v>2</v>
       </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -9841,6 +11083,16 @@
       <c r="S107" t="n">
         <v>2</v>
       </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -9914,6 +11166,16 @@
       <c r="S108" t="n">
         <v>2</v>
       </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -9986,6 +11248,16 @@
       </c>
       <c r="S109" t="n">
         <v>2</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -10048,6 +11320,16 @@
       <c r="S110" t="n">
         <v>1</v>
       </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10109,6 +11391,16 @@
       <c r="S111" t="n">
         <v>1</v>
       </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10170,6 +11462,16 @@
       <c r="S112" t="n">
         <v>1</v>
       </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10231,6 +11533,16 @@
       <c r="S113" t="n">
         <v>1</v>
       </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10292,6 +11604,16 @@
       <c r="S114" t="n">
         <v>1</v>
       </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10353,6 +11675,16 @@
       <c r="S115" t="n">
         <v>1</v>
       </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10414,6 +11746,16 @@
       <c r="S116" t="n">
         <v>1</v>
       </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10475,6 +11817,16 @@
       <c r="S117" t="n">
         <v>1</v>
       </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10536,6 +11888,16 @@
       <c r="S118" t="n">
         <v>1</v>
       </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10597,6 +11959,16 @@
       <c r="S119" t="n">
         <v>1</v>
       </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10658,6 +12030,16 @@
       <c r="S120" t="n">
         <v>1</v>
       </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -10719,6 +12101,16 @@
       <c r="S121" t="n">
         <v>1</v>
       </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10792,6 +12184,16 @@
       <c r="S122" t="n">
         <v>1</v>
       </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10865,6 +12267,16 @@
       <c r="S123" t="n">
         <v>1</v>
       </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -10938,6 +12350,16 @@
       <c r="S124" t="n">
         <v>1</v>
       </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11011,6 +12433,16 @@
       <c r="S125" t="n">
         <v>1</v>
       </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -11080,6 +12512,16 @@
       <c r="S126" t="n">
         <v>1</v>
       </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11149,6 +12591,16 @@
       <c r="S127" t="n">
         <v>1</v>
       </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -11218,6 +12670,16 @@
       <c r="S128" t="n">
         <v>1</v>
       </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11287,6 +12749,16 @@
       <c r="S129" t="n">
         <v>1</v>
       </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11356,6 +12828,16 @@
       <c r="S130" t="n">
         <v>1</v>
       </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11422,6 +12904,16 @@
       </c>
       <c r="S131" t="n">
         <v>1</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -11484,6 +12976,16 @@
       <c r="S132" t="n">
         <v>1</v>
       </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -11545,6 +13047,16 @@
       <c r="S133" t="n">
         <v>1</v>
       </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11606,6 +13118,16 @@
       <c r="S134" t="n">
         <v>1</v>
       </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11667,6 +13189,16 @@
       <c r="S135" t="n">
         <v>1</v>
       </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11732,6 +13264,16 @@
       <c r="S136" t="n">
         <v>1</v>
       </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -11797,6 +13339,16 @@
       <c r="S137" t="n">
         <v>1</v>
       </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -11862,6 +13414,16 @@
       <c r="S138" t="n">
         <v>1</v>
       </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11927,6 +13489,16 @@
       <c r="S139" t="n">
         <v>1</v>
       </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11992,6 +13564,16 @@
       <c r="S140" t="n">
         <v>1</v>
       </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -12057,6 +13639,16 @@
       <c r="S141" t="n">
         <v>1</v>
       </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -12122,6 +13714,16 @@
       <c r="S142" t="n">
         <v>1</v>
       </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -12187,6 +13789,16 @@
       <c r="S143" t="n">
         <v>1</v>
       </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -12252,6 +13864,16 @@
       <c r="S144" t="n">
         <v>1</v>
       </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -12313,6 +13935,16 @@
       <c r="S145" t="n">
         <v>1</v>
       </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -12374,6 +14006,16 @@
       <c r="S146" t="n">
         <v>1</v>
       </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -12439,6 +14081,16 @@
       <c r="S147" t="n">
         <v>1</v>
       </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -12500,6 +14152,16 @@
       <c r="S148" t="n">
         <v>1</v>
       </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -12561,6 +14223,16 @@
       <c r="S149" t="n">
         <v>1</v>
       </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -12622,6 +14294,16 @@
       <c r="S150" t="n">
         <v>1</v>
       </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -12683,6 +14365,16 @@
       <c r="S151" t="n">
         <v>1</v>
       </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -12746,6 +14438,16 @@
       <c r="S152" t="n">
         <v>1</v>
       </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12809,6 +14511,16 @@
       <c r="S153" t="n">
         <v>1</v>
       </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12872,6 +14584,16 @@
       <c r="S154" t="n">
         <v>1</v>
       </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12934,6 +14656,16 @@
       </c>
       <c r="S155" t="n">
         <v>1</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -12980,6 +14712,16 @@
       <c r="S156" t="n">
         <v>1</v>
       </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-4o)</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13036,6 +14778,16 @@
       </c>
       <c r="S157" t="n">
         <v>1</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -13090,6 +14842,16 @@
       <c r="S158" t="n">
         <v>1</v>
       </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -13143,6 +14905,16 @@
       <c r="S159" t="n">
         <v>1</v>
       </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -13196,6 +14968,16 @@
       <c r="S160" t="n">
         <v>1</v>
       </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -13269,6 +15051,16 @@
       <c r="S161" t="n">
         <v>1</v>
       </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -13340,6 +15132,16 @@
       <c r="S162" t="n">
         <v>1</v>
       </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -13413,6 +15215,16 @@
       <c r="S163" t="n">
         <v>1</v>
       </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -13486,6 +15298,16 @@
       <c r="S164" t="n">
         <v>1</v>
       </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -13558,6 +15380,16 @@
       </c>
       <c r="S165" t="n">
         <v>1</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -13620,6 +15452,16 @@
       <c r="S166" t="n">
         <v>1</v>
       </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -13681,6 +15523,16 @@
       <c r="S167" t="n">
         <v>1</v>
       </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -13742,6 +15594,16 @@
       <c r="S168" t="n">
         <v>1</v>
       </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -13815,6 +15677,16 @@
       <c r="S169" t="n">
         <v>1</v>
       </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13884,6 +15756,16 @@
       <c r="S170" t="n">
         <v>1</v>
       </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13957,6 +15839,16 @@
       <c r="S171" t="n">
         <v>1</v>
       </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -14030,6 +15922,16 @@
       <c r="S172" t="n">
         <v>1</v>
       </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -14097,6 +15999,16 @@
       <c r="S173" t="n">
         <v>1</v>
       </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -14164,6 +16076,16 @@
       <c r="S174" t="n">
         <v>1</v>
       </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -14231,6 +16153,16 @@
       <c r="S175" t="n">
         <v>1</v>
       </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -14298,6 +16230,16 @@
       <c r="S176" t="n">
         <v>1</v>
       </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -14367,6 +16309,16 @@
       <c r="S177" t="n">
         <v>1</v>
       </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -14436,6 +16388,16 @@
       <c r="S178" t="n">
         <v>1</v>
       </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -14505,6 +16467,16 @@
       <c r="S179" t="n">
         <v>1</v>
       </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -14574,6 +16546,16 @@
       <c r="S180" t="n">
         <v>1</v>
       </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -14643,6 +16625,16 @@
       <c r="S181" t="n">
         <v>1</v>
       </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -14711,6 +16703,16 @@
       </c>
       <c r="S182" t="n">
         <v>1</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -14773,6 +16775,16 @@
       <c r="S183" t="n">
         <v>1</v>
       </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -14834,6 +16846,16 @@
       <c r="S184" t="n">
         <v>1</v>
       </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -14895,6 +16917,16 @@
       <c r="S185" t="n">
         <v>1</v>
       </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -14956,6 +16988,16 @@
       <c r="S186" t="n">
         <v>1</v>
       </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -15017,6 +17059,16 @@
       <c r="S187" t="n">
         <v>1</v>
       </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -15078,6 +17130,16 @@
       <c r="S188" t="n">
         <v>1</v>
       </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -15139,6 +17201,16 @@
       <c r="S189" t="n">
         <v>1</v>
       </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -15200,6 +17272,16 @@
       <c r="S190" t="n">
         <v>1</v>
       </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -15261,6 +17343,16 @@
       <c r="S191" t="n">
         <v>1</v>
       </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -15322,6 +17414,16 @@
       <c r="S192" t="n">
         <v>1</v>
       </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -15382,6 +17484,16 @@
       </c>
       <c r="S193" t="n">
         <v>1</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -15440,6 +17552,16 @@
       <c r="S194" t="n">
         <v>1</v>
       </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -15509,6 +17631,16 @@
       <c r="S195" t="n">
         <v>1</v>
       </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -15578,6 +17710,16 @@
       <c r="S196" t="n">
         <v>1</v>
       </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -15647,6 +17789,16 @@
       <c r="S197" t="n">
         <v>1</v>
       </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -15720,6 +17872,16 @@
       <c r="S198" t="n">
         <v>1</v>
       </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -15793,6 +17955,16 @@
       <c r="S199" t="n">
         <v>1</v>
       </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -15862,6 +18034,16 @@
       <c r="S200" t="n">
         <v>1</v>
       </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -15931,6 +18113,16 @@
       <c r="S201" t="n">
         <v>1</v>
       </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -16000,6 +18192,16 @@
       <c r="S202" t="n">
         <v>1</v>
       </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -16069,6 +18271,16 @@
       <c r="S203" t="n">
         <v>1</v>
       </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -16138,6 +18350,16 @@
       <c r="S204" t="n">
         <v>1</v>
       </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -16207,6 +18429,16 @@
       <c r="S205" t="n">
         <v>1</v>
       </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -16273,6 +18505,16 @@
       </c>
       <c r="S206" t="n">
         <v>1</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -16333,6 +18575,16 @@
       <c r="S207" t="n">
         <v>1</v>
       </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -16398,6 +18650,16 @@
       <c r="S208" t="n">
         <v>1</v>
       </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -16466,6 +18728,16 @@
       </c>
       <c r="S209" t="n">
         <v>1</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -16526,6 +18798,16 @@
       <c r="S210" t="n">
         <v>1</v>
       </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -16585,6 +18867,16 @@
       <c r="S211" t="n">
         <v>1</v>
       </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -16653,6 +18945,16 @@
       </c>
       <c r="S212" t="n">
         <v>1</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -16712,6 +19014,16 @@
       </c>
       <c r="S213" t="n">
         <v>1</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -16770,6 +19082,16 @@
       <c r="S214" t="n">
         <v>1</v>
       </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -16827,6 +19149,16 @@
       <c r="S215" t="n">
         <v>1</v>
       </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -16883,6 +19215,16 @@
       </c>
       <c r="S216" t="n">
         <v>1</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -16929,6 +19271,16 @@
       <c r="S217" t="n">
         <v>1</v>
       </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -16994,6 +19346,16 @@
       <c r="S218" t="n">
         <v>1</v>
       </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -17059,6 +19421,16 @@
       <c r="S219" t="n">
         <v>1</v>
       </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -17120,6 +19492,16 @@
       <c r="S220" t="n">
         <v>1</v>
       </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -17180,6 +19562,16 @@
       </c>
       <c r="S221" t="n">
         <v>1</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -17244,6 +19636,16 @@
       <c r="S222" t="n">
         <v>1</v>
       </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -17307,6 +19709,16 @@
       <c r="S223" t="n">
         <v>1</v>
       </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -17370,6 +19782,16 @@
       <c r="S224" t="n">
         <v>1</v>
       </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -17433,6 +19855,16 @@
       <c r="S225" t="n">
         <v>1</v>
       </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -17496,6 +19928,16 @@
       <c r="S226" t="n">
         <v>1</v>
       </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -17559,6 +20001,16 @@
       <c r="S227" t="n">
         <v>1</v>
       </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -17622,6 +20074,16 @@
       <c r="S228" t="n">
         <v>1</v>
       </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -17685,6 +20147,16 @@
       <c r="S229" t="n">
         <v>1</v>
       </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -17748,6 +20220,16 @@
       <c r="S230" t="n">
         <v>1</v>
       </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -17811,6 +20293,16 @@
       <c r="S231" t="n">
         <v>1</v>
       </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -17874,6 +20366,16 @@
       <c r="S232" t="n">
         <v>1</v>
       </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -17937,6 +20439,16 @@
       <c r="S233" t="n">
         <v>1</v>
       </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -18010,6 +20522,16 @@
       <c r="S234" t="n">
         <v>1</v>
       </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -18083,6 +20605,16 @@
       <c r="S235" t="n">
         <v>1</v>
       </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -18156,6 +20688,16 @@
       <c r="S236" t="n">
         <v>1</v>
       </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -18225,6 +20767,16 @@
       <c r="S237" t="n">
         <v>1</v>
       </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -18294,6 +20846,16 @@
       <c r="S238" t="n">
         <v>1</v>
       </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -18367,6 +20929,16 @@
       <c r="S239" t="n">
         <v>1</v>
       </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -18440,6 +21012,16 @@
       <c r="S240" t="n">
         <v>1</v>
       </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -18511,6 +21093,16 @@
       <c r="S241" t="n">
         <v>1</v>
       </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -18584,6 +21176,16 @@
       <c r="S242" t="n">
         <v>1</v>
       </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -18655,6 +21257,16 @@
       <c r="S243" t="n">
         <v>1</v>
       </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -18726,6 +21338,16 @@
       <c r="S244" t="n">
         <v>1</v>
       </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -18797,6 +21419,16 @@
       <c r="S245" t="n">
         <v>1</v>
       </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -18870,6 +21502,16 @@
       <c r="S246" t="n">
         <v>1</v>
       </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -18943,6 +21585,16 @@
       <c r="S247" t="n">
         <v>1</v>
       </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -19016,6 +21668,16 @@
       <c r="S248" t="n">
         <v>1</v>
       </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -19089,6 +21751,16 @@
       <c r="S249" t="n">
         <v>1</v>
       </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -19161,6 +21833,16 @@
       </c>
       <c r="S250" t="n">
         <v>1</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -19215,6 +21897,16 @@
       <c r="S251" t="n">
         <v>1</v>
       </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -19280,6 +21972,16 @@
       <c r="S252" t="n">
         <v>1</v>
       </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -19349,6 +22051,16 @@
       <c r="S253" t="n">
         <v>1</v>
       </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -19418,6 +22130,16 @@
       <c r="S254" t="n">
         <v>1</v>
       </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -19487,6 +22209,16 @@
       <c r="S255" t="n">
         <v>1</v>
       </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -19556,6 +22288,16 @@
       <c r="S256" t="n">
         <v>1</v>
       </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -19625,6 +22367,16 @@
       <c r="S257" t="n">
         <v>1</v>
       </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -19694,6 +22446,16 @@
       <c r="S258" t="n">
         <v>1</v>
       </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -19763,6 +22525,16 @@
       <c r="S259" t="n">
         <v>1</v>
       </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -19832,6 +22604,16 @@
       <c r="S260" t="n">
         <v>1</v>
       </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -19905,6 +22687,16 @@
       <c r="S261" t="n">
         <v>1</v>
       </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -19978,6 +22770,16 @@
       <c r="S262" t="n">
         <v>1</v>
       </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -20051,6 +22853,16 @@
       <c r="S263" t="n">
         <v>1</v>
       </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -20124,6 +22936,16 @@
       <c r="S264" t="n">
         <v>1</v>
       </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -20197,6 +23019,16 @@
       <c r="S265" t="n">
         <v>1</v>
       </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -20270,6 +23102,16 @@
       <c r="S266" t="n">
         <v>1</v>
       </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -20343,6 +23185,16 @@
       <c r="S267" t="n">
         <v>1</v>
       </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -20412,6 +23264,16 @@
       <c r="S268" t="n">
         <v>1</v>
       </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>GPT-3.5-turbo</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -20481,6 +23343,16 @@
       <c r="S269" t="n">
         <v>1</v>
       </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>GPT-3.5-turbo</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -20550,6 +23422,16 @@
       <c r="S270" t="n">
         <v>1</v>
       </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>GPT-3.5-turbo</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -20619,6 +23501,16 @@
       <c r="S271" t="n">
         <v>1</v>
       </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>GPT-3.5-turbo</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -20689,6 +23581,16 @@
       </c>
       <c r="S272" t="n">
         <v>1</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -20747,6 +23649,16 @@
       <c r="S273" t="n">
         <v>1</v>
       </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -20808,6 +23720,16 @@
       <c r="S274" t="n">
         <v>1</v>
       </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -20873,6 +23795,16 @@
       <c r="S275" t="n">
         <v>1</v>
       </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -20934,6 +23866,16 @@
       <c r="S276" t="n">
         <v>1</v>
       </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -20995,6 +23937,16 @@
       <c r="S277" t="n">
         <v>1</v>
       </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -21056,6 +24008,16 @@
       <c r="S278" t="n">
         <v>1</v>
       </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -21117,6 +24079,16 @@
       <c r="S279" t="n">
         <v>1</v>
       </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -21182,6 +24154,16 @@
       <c r="S280" t="n">
         <v>1</v>
       </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -21247,6 +24229,16 @@
       <c r="S281" t="n">
         <v>1</v>
       </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -21312,6 +24304,16 @@
       <c r="S282" t="n">
         <v>1</v>
       </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -21373,6 +24375,16 @@
       <c r="S283" t="n">
         <v>1</v>
       </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -21434,6 +24446,16 @@
       <c r="S284" t="n">
         <v>1</v>
       </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -21495,6 +24517,16 @@
       <c r="S285" t="n">
         <v>1</v>
       </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -21556,6 +24588,16 @@
       <c r="S286" t="n">
         <v>1</v>
       </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -21620,6 +24662,16 @@
       </c>
       <c r="S287" t="n">
         <v>1</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -21682,6 +24734,16 @@
       <c r="S288" t="n">
         <v>1</v>
       </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -21743,6 +24805,16 @@
       <c r="S289" t="n">
         <v>1</v>
       </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -21804,6 +24876,16 @@
       <c r="S290" t="n">
         <v>1</v>
       </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -21871,6 +24953,16 @@
       <c r="S291" t="n">
         <v>1</v>
       </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -21936,6 +25028,16 @@
       <c r="S292" t="n">
         <v>1</v>
       </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -22001,6 +25103,16 @@
       <c r="S293" t="n">
         <v>1</v>
       </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -22070,6 +25182,16 @@
       <c r="S294" t="n">
         <v>1</v>
       </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -22143,6 +25265,16 @@
       <c r="S295" t="n">
         <v>1</v>
       </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -22216,6 +25348,16 @@
       <c r="S296" t="n">
         <v>1</v>
       </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -22289,6 +25431,16 @@
       <c r="S297" t="n">
         <v>1</v>
       </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -22362,6 +25514,16 @@
       <c r="S298" t="n">
         <v>1</v>
       </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -22435,6 +25597,16 @@
       <c r="S299" t="n">
         <v>1</v>
       </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -22503,6 +25675,16 @@
       </c>
       <c r="S300" t="n">
         <v>1</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -22559,6 +25741,16 @@
       <c r="S301" t="n">
         <v>1</v>
       </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -22618,6 +25810,16 @@
       <c r="S302" t="n">
         <v>1</v>
       </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -22677,6 +25879,16 @@
       <c r="S303" t="n">
         <v>1</v>
       </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -22731,6 +25943,16 @@
       </c>
       <c r="S304" t="n">
         <v>1</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -22777,6 +25999,16 @@
       <c r="S305" t="n">
         <v>1</v>
       </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -22822,6 +26054,16 @@
       <c r="S306" t="n">
         <v>1</v>
       </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -22883,6 +26125,16 @@
       <c r="S307" t="n">
         <v>1</v>
       </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -22948,6 +26200,16 @@
       <c r="S308" t="n">
         <v>1</v>
       </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -23013,6 +26275,16 @@
       <c r="S309" t="n">
         <v>1</v>
       </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -23078,6 +26350,16 @@
       <c r="S310" t="n">
         <v>1</v>
       </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -23139,6 +26421,16 @@
       <c r="S311" t="n">
         <v>1</v>
       </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -23204,6 +26496,16 @@
       <c r="S312" t="n">
         <v>1</v>
       </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -23269,6 +26571,16 @@
       <c r="S313" t="n">
         <v>1</v>
       </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -23334,6 +26646,16 @@
       <c r="S314" t="n">
         <v>1</v>
       </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -23399,6 +26721,16 @@
       <c r="S315" t="n">
         <v>1</v>
       </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -23464,6 +26796,16 @@
       <c r="S316" t="n">
         <v>1</v>
       </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -23525,6 +26867,16 @@
       <c r="S317" t="n">
         <v>1</v>
       </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -23586,6 +26938,16 @@
       <c r="S318" t="n">
         <v>1</v>
       </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -23655,6 +27017,16 @@
       <c r="S319" t="n">
         <v>1</v>
       </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -23723,6 +27095,16 @@
       </c>
       <c r="S320" t="n">
         <v>1</v>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -23769,6 +27151,16 @@
       <c r="S321" t="n">
         <v>1</v>
       </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -23838,6 +27230,16 @@
       <c r="S322" t="n">
         <v>1</v>
       </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -23906,6 +27308,16 @@
       </c>
       <c r="S323" t="n">
         <v>1</v>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -23964,6 +27376,16 @@
       <c r="S324" t="n">
         <v>1</v>
       </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -24024,6 +27446,16 @@
       </c>
       <c r="S325" t="n">
         <v>1</v>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -24082,6 +27514,16 @@
       <c r="S326" t="n">
         <v>1</v>
       </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -24139,6 +27581,16 @@
       <c r="S327" t="n">
         <v>1</v>
       </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -24196,6 +27648,16 @@
       <c r="S328" t="n">
         <v>1</v>
       </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -24252,6 +27714,16 @@
       </c>
       <c r="S329" t="n">
         <v>1</v>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -24306,6 +27778,16 @@
       <c r="S330" t="n">
         <v>1</v>
       </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -24367,6 +27849,16 @@
       <c r="S331" t="n">
         <v>1</v>
       </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -24428,6 +27920,16 @@
       <c r="S332" t="n">
         <v>1</v>
       </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -24489,6 +27991,16 @@
       <c r="S333" t="n">
         <v>1</v>
       </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -24550,6 +28062,16 @@
       <c r="S334" t="n">
         <v>1</v>
       </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -24611,6 +28133,16 @@
       <c r="S335" t="n">
         <v>1</v>
       </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -24672,6 +28204,16 @@
       <c r="S336" t="n">
         <v>1</v>
       </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -24737,6 +28279,16 @@
       <c r="S337" t="n">
         <v>1</v>
       </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -24802,6 +28354,16 @@
       <c r="S338" t="n">
         <v>1</v>
       </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -24865,6 +28427,16 @@
       <c r="S339" t="n">
         <v>1</v>
       </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -24930,6 +28502,16 @@
       <c r="S340" t="n">
         <v>1</v>
       </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -24995,6 +28577,16 @@
       <c r="S341" t="n">
         <v>1</v>
       </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -25057,6 +28649,16 @@
       </c>
       <c r="S342" t="n">
         <v>1</v>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -25099,6 +28701,16 @@
       <c r="S343" t="n">
         <v>3</v>
       </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -25166,6 +28778,16 @@
       <c r="S344" t="n">
         <v>1</v>
       </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -25239,6 +28861,8 @@
       <c r="S345" t="n">
         <v>1</v>
       </c>
+      <c r="T345" t="inlineStr"/>
+      <c r="U345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -25308,6 +28932,8 @@
       <c r="S346" t="n">
         <v>1</v>
       </c>
+      <c r="T346" t="inlineStr"/>
+      <c r="U346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -25377,6 +29003,8 @@
       <c r="S347" t="n">
         <v>1</v>
       </c>
+      <c r="T347" t="inlineStr"/>
+      <c r="U347" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25389,7 +29017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25737,30 +29365,270 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Overall</t>
+          <t>GenAI_Tool</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>All Studies</t>
+          <t>not_reported</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>346</v>
+        <v>170</v>
       </c>
       <c r="E12" t="n">
-        <v>0.844</v>
+        <v>0.861</v>
       </c>
       <c r="F12" t="n">
-        <v>1.268</v>
+        <v>1.351</v>
       </c>
       <c r="G12" t="n">
         <v>-3.033</v>
       </c>
       <c r="H12" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GenAI_Tool</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>39</v>
+      </c>
+      <c r="D13" t="n">
+        <v>151</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.072</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.078</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GenAI_Tool</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ChatGPT (gpt-3.5-turbo-16k)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.255</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.645</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GenAI_Tool</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GPT-3.5-turbo</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.622</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GenAI_Tool</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.444</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Study_Design</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-3.033</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.869999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Study_Design</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D18" t="n">
+        <v>62</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.072</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.444</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Study_Design</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" t="n">
+        <v>98</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.255</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.078</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All Studies</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>61</v>
+      </c>
+      <c r="D20" t="n">
+        <v>346</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.033</v>
+      </c>
+      <c r="H20" t="n">
         <v>9.869999999999999</v>
       </c>
     </row>
